--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487449_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487449_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>G. PREOTU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1628</v>
+        <v>1.5255</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6637</v>
+        <v>2.5865</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5009</v>
+        <v>-1.061</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5733</v>
+        <v>-0.438</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3062</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3722</v>
+        <v>0.1557</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6447000000000001</v>
+        <v>-0.3437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7275</v>
+        <v>0.4994</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.799</v>
+        <v>-0.5938</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.951</v>
+        <v>-0.6093</v>
       </c>
       <c r="O2" t="n">
-        <v>0.152</v>
+        <v>0.0156</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6311</v>
+        <v>0.1789</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0161</v>
+        <v>0.721</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.385</v>
+        <v>-0.5421</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2166</v>
+        <v>0.2178</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2754</v>
+        <v>1.7097</v>
       </c>
       <c r="X2" t="n">
         <v>-1.492</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PREOTU</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8056</v>
+        <v>1.3444</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1607</v>
+        <v>2.8185</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3551</v>
+        <v>-1.4741</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.438</v>
+        <v>0.5733</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.3062</v>
       </c>
       <c r="I3" t="n">
-        <v>0.515</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1557</v>
+        <v>1.3722</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3437</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4994</v>
+        <v>0.7275</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5938</v>
+        <v>-0.799</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6093</v>
+        <v>-0.951</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0156</v>
+        <v>0.152</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5409</v>
+        <v>0.8127</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2952</v>
+        <v>1.171</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8361</v>
+        <v>-0.3583</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2178</v>
+        <v>-1.2166</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7097</v>
+        <v>0.2754</v>
       </c>
       <c r="X3" t="n">
         <v>-1.492</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6038</v>
+        <v>0.9873</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2925</v>
+        <v>-0.501</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8963</v>
+        <v>1.4884</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6106</v>
+        <v>-1.8917</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4779</v>
+        <v>-3.5391</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1327</v>
+        <v>1.6474</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9678</v>
+        <v>-1.6562</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6054</v>
+        <v>-2.9995</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5732</v>
+        <v>1.3433</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6428</v>
+        <v>-0.2355</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0833</v>
+        <v>-0.5395</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4405</v>
+        <v>0.304</v>
       </c>
       <c r="P4" t="n">
         <v>-0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2513</v>
+        <v>0.9171</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2374</v>
+        <v>0.6805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0138</v>
+        <v>0.2366</v>
       </c>
       <c r="V4" t="n">
-        <v>1.159</v>
+        <v>2.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3756</v>
+        <v>2.4332</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1108</v>
+        <v>0.9751</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1671</v>
+        <v>-0.0549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2779</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2092</v>
+        <v>-1.6106</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.557</v>
+        <v>-0.4779</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3478</v>
+        <v>-1.1327</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7529</v>
+        <v>-0.9678</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5393</v>
+        <v>0.6054</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2136</v>
+        <v>-1.5732</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4563</v>
+        <v>-0.6428</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0176</v>
+        <v>-1.0833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5614</v>
+        <v>0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1543</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6576</v>
+        <v>1.6225</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5858</v>
+        <v>1.475</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0718</v>
+        <v>0.1475</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.492</v>
+        <v>1.159</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.3756</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4807</v>
+        <v>0.8458</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3166</v>
+        <v>0.1134</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8359</v>
+        <v>0.7323</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8917</v>
+        <v>-1.2092</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.5391</v>
+        <v>-1.557</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6474</v>
+        <v>0.3478</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6562</v>
+        <v>-0.7529</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.9995</v>
+        <v>-0.5393</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3433</v>
+        <v>-0.2136</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2355</v>
+        <v>-0.4563</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5395</v>
+        <v>-1.0176</v>
       </c>
       <c r="O6" t="n">
-        <v>0.304</v>
+        <v>0.5614</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.551</v>
+        <v>1.3926</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1351</v>
+        <v>0.8663</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5841</v>
+        <v>0.5262</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1578</v>
+        <v>-1.492</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5692</v>
+        <v>-0.9769</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.368</v>
+        <v>-3.6421</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7988</v>
+        <v>2.6651</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7832</v>
@@ -1000,13 +1000,13 @@
         <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6046</v>
+        <v>2.1968</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0385</v>
+        <v>1.7644</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5661</v>
+        <v>0.4324</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9988</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7203</v>
+        <v>-2.6002</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6364</v>
+        <v>-3.0887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9161</v>
+        <v>0.4884</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5511</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2433</v>
+        <v>1.3633</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1492</v>
+        <v>0.6969</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0941</v>
+        <v>0.6664</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2166</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9127999999999998</v>
+        <v>2.101</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.956199999999999</v>
+        <v>-1.7683</v>
       </c>
       <c r="F9" t="n">
-        <v>3.869000000000001</v>
+        <v>3.8691</v>
       </c>
       <c r="G9" t="n">
         <v>-8.910499999999999</v>
@@ -1126,7 +1126,7 @@
         <v>-8.858799999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05190000000000028</v>
+        <v>-0.05189999999999984</v>
       </c>
       <c r="J9" t="n">
         <v>-5.6967</v>
@@ -1141,7 +1141,7 @@
         <v>-3.214</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.4162</v>
+        <v>-5.416199999999999</v>
       </c>
       <c r="O9" t="n">
         <v>2.2025</v>
@@ -1156,19 +1156,19 @@
         <v>13.7093</v>
       </c>
       <c r="S9" t="n">
-        <v>7.295999999999999</v>
+        <v>8.4839</v>
       </c>
       <c r="T9" t="n">
-        <v>6.187100000000001</v>
+        <v>7.3751</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1088</v>
+        <v>1.1087</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3894</v>
       </c>
       <c r="W9" t="n">
-        <v>6.345799999999999</v>
+        <v>6.345800000000001</v>
       </c>
       <c r="X9" t="n">
         <v>-7.7353</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.8995</v>
+        <v>9.5733</v>
       </c>
       <c r="E10" t="n">
         <v>6.2759</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6236</v>
+        <v>3.2975</v>
       </c>
       <c r="G10" t="n">
         <v>6.8435</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4359</v>
+        <v>-0.7621</v>
       </c>
       <c r="T10" t="n">
         <v>0.0576</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4936</v>
+        <v>-0.8197</v>
       </c>
       <c r="V10" t="n">
         <v>2.7086</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8545</v>
+        <v>2.9279</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3016</v>
+        <v>2.9712</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4471</v>
+        <v>-0.0433</v>
       </c>
       <c r="G11" t="n">
         <v>2.3542</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4415</v>
+        <v>0.5149</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4319</v>
+        <v>1.1016</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.5867</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3329</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.997</v>
+        <v>2.1215</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9357</v>
+        <v>1.1403</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0613</v>
+        <v>0.9811</v>
       </c>
       <c r="G12" t="n">
         <v>0.6503</v>
@@ -1390,13 +1390,13 @@
         <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4563</v>
+        <v>-0.3319</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2781</v>
+        <v>-0.3583</v>
       </c>
       <c r="V12" t="n">
         <v>1.6071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1682</v>
+        <v>1.5941</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9541</v>
+        <v>3.0564</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7859</v>
+        <v>-1.4623</v>
       </c>
       <c r="G13" t="n">
         <v>2.8677</v>
@@ -1468,13 +1468,13 @@
         <v>0.5875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.1734</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.421</v>
+        <v>-0.0975</v>
       </c>
       <c r="V13" t="n">
         <v>-1.492</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>P. DIAZ VALIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9217</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.987</v>
+        <v>-0.3445</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9087</v>
+        <v>0.987</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9913999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7749</v>
+        <v>0.4427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7835</v>
+        <v>0.4954</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.436</v>
+        <v>0.1131</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.0519</v>
+        <v>0.0323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6159</v>
+        <v>0.0808</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4446</v>
+        <v>0.8249</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2771</v>
+        <v>0.4104</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1676</v>
+        <v>0.4145</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7172</v>
+        <v>-0.1364</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.18</v>
+        <v>-0.0659</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8972</v>
+        <v>-0.0706</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. DIAZ VALIN</t>
+          <t>A. GOMEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1263</v>
+        <v>0.3293</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7538</v>
+        <v>0.3713</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8801</v>
+        <v>-0.042</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.4019</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4427</v>
+        <v>1.1539</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4954</v>
+        <v>0.2481</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1131</v>
+        <v>1.8499</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0323</v>
+        <v>1.082</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0808</v>
+        <v>0.7679</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8249</v>
+        <v>-0.448</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4104</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4145</v>
+        <v>-0.5198</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-1.151</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4752</v>
+        <v>-0.3035</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1775</v>
+        <v>-0.8475</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5507</v>
+        <v>0.6659</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5507</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GOMEZ VAZQUEZ</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5373</v>
+        <v>-0.5218</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.038</v>
+        <v>-3.3963</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4993</v>
+        <v>2.8745</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4019</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1539</v>
+        <v>-1.7749</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2481</v>
+        <v>0.7835</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8499</v>
+        <v>-1.436</v>
       </c>
       <c r="K16" t="n">
-        <v>1.082</v>
+        <v>-2.0519</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7679</v>
+        <v>0.6159</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.448</v>
+        <v>0.4446</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.2771</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5198</v>
+        <v>0.1676</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1751</v>
+        <v>-1.3709</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0175</v>
+        <v>0.2738</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7128</v>
+        <v>-0.5893</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3047</v>
+        <v>0.8631</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>É. PINA HURTADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4847</v>
+        <v>-1.5132</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.735</v>
+        <v>-1.6623</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7497</v>
+        <v>0.1491</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8384</v>
+        <v>-0.1086</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8891</v>
+        <v>0.4825</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0508</v>
+        <v>-0.591</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5968</v>
+        <v>-1.2803</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9516</v>
+        <v>0.0033</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3548</v>
+        <v>-1.2836</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2415</v>
+        <v>1.1717</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0625</v>
+        <v>0.4791</v>
       </c>
       <c r="O17" t="n">
-        <v>0.304</v>
+        <v>0.6926</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9792</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.546</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1272</v>
+        <v>0.1622</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0612</v>
+        <v>0.3599</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.066</v>
+        <v>-0.1978</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="X17" t="n">
         <v>-1.2166</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>É. PINA HURTADO</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3927</v>
+        <v>-1.5723</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3786</v>
+        <v>-1.042</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0141</v>
+        <v>-0.5302</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1086</v>
+        <v>1.8384</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4825</v>
+        <v>2.8891</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.591</v>
+        <v>-1.0508</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2803</v>
+        <v>1.5968</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0033</v>
+        <v>2.9516</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2836</v>
+        <v>-1.3548</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1717</v>
+        <v>0.2415</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4791</v>
+        <v>-0.0625</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6926</v>
+        <v>0.304</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-2.546</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7173</v>
+        <v>-1.2148</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3564</v>
+        <v>-0.3682</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3609</v>
+        <v>-0.8466</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2166</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0355</v>
+        <v>-2.8797</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3827</v>
+        <v>-2.2804</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6528</v>
+        <v>-0.5994</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8336</v>
@@ -1936,13 +1936,13 @@
         <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3978</v>
+        <v>-0.242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0414</v>
+        <v>0.0121</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8965</v>
+        <v>-4.5332</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5382</v>
+        <v>-4.2312</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3583</v>
+        <v>-0.302</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9502</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6169</v>
+        <v>-0.2536</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5346</v>
+        <v>-0.2276</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0823</v>
+        <v>-0.026</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5333</v>
+        <v>-5.0346</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.523</v>
+        <v>-4.7277</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0103</v>
+        <v>-0.3069</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0998</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4335</v>
+        <v>-1.9348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5652</v>
+        <v>-0.7699</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8683</v>
+        <v>-1.1649</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9127999999999998</v>
+        <v>1.133899999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.868999999999998</v>
+        <v>-3.869300000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9562</v>
+        <v>5.003100000000001</v>
       </c>
       <c r="G22" t="n">
         <v>8.910399999999999</v>
@@ -2143,16 +2143,16 @@
         <v>0.05200000000000049</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2138</v>
+        <v>3.213800000000002</v>
       </c>
       <c r="K22" t="n">
-        <v>5.416100000000001</v>
+        <v>5.416099999999999</v>
       </c>
       <c r="L22" t="n">
         <v>-2.2024</v>
       </c>
       <c r="M22" t="n">
-        <v>5.6966</v>
+        <v>5.696600000000001</v>
       </c>
       <c r="N22" t="n">
         <v>3.442399999999999</v>
@@ -2167,16 +2167,16 @@
         <v>-13.7092</v>
       </c>
       <c r="R22" t="n">
-        <v>9.792200000000001</v>
+        <v>9.792199999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.2957</v>
+        <v>-5.2491</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1087</v>
+        <v>-1.1088</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.187000000000001</v>
+        <v>-4.140400000000001</v>
       </c>
       <c r="V22" t="n">
         <v>1.3894</v>
